--- a/data/current_report.xlsx
+++ b/data/current_report.xlsx
@@ -1389,50 +1389,6 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1333500" cy="1257300"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>923925</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -3049,10 +3005,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O24" s="16">
         <v>0</v>
@@ -3064,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="R24" s="16">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S24" s="16">
         <v>0</v>
@@ -3073,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V24" s="16">
         <v>0</v>
@@ -3085,13 +3041,13 @@
         <v>0</v>
       </c>
       <c r="Y24" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z24" s="16">
         <v>0</v>
       </c>
       <c r="AA24" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" s="16">
         <v>0</v>
@@ -3155,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="16">
         <v>0</v>
@@ -3167,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="R25" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="16">
         <v>0</v>
@@ -3176,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="16">
         <v>0</v>
@@ -3409,16 +3365,16 @@
         <v>0</v>
       </c>
       <c r="E29" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="16">
         <v>0</v>
@@ -3427,38 +3383,38 @@
         <v>0</v>
       </c>
       <c r="K29" s="16">
+        <v>5</v>
+      </c>
+      <c r="L29" s="16">
+        <v>0</v>
+      </c>
+      <c r="M29" s="16">
+        <v>0</v>
+      </c>
+      <c r="N29" s="16">
+        <v>1</v>
+      </c>
+      <c r="O29" s="16">
+        <v>4</v>
+      </c>
+      <c r="P29" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="16">
+        <v>0</v>
+      </c>
+      <c r="R29" s="16">
+        <v>0</v>
+      </c>
+      <c r="S29" s="16">
+        <v>0</v>
+      </c>
+      <c r="T29" s="16">
+        <v>0</v>
+      </c>
+      <c r="U29" s="16">
         <v>3</v>
       </c>
-      <c r="L29" s="16">
-        <v>0</v>
-      </c>
-      <c r="M29" s="16">
-        <v>0</v>
-      </c>
-      <c r="N29" s="16">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16">
-        <v>0</v>
-      </c>
-      <c r="P29" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="16">
-        <v>0</v>
-      </c>
-      <c r="R29" s="16">
-        <v>0</v>
-      </c>
-      <c r="S29" s="16">
-        <v>0</v>
-      </c>
-      <c r="T29" s="16">
-        <v>0</v>
-      </c>
-      <c r="U29" s="16">
-        <v>0</v>
-      </c>
       <c r="V29" s="16">
         <v>0</v>
       </c>
@@ -3469,16 +3425,16 @@
         <v>0</v>
       </c>
       <c r="Y29" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z29" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" s="16">
         <v>0</v>
@@ -3512,13 +3468,13 @@
         <v>0</v>
       </c>
       <c r="E30" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="16">
         <v>0</v>
@@ -3539,10 +3495,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30" s="16">
         <v>0</v>
@@ -3557,10 +3513,10 @@
         <v>0</v>
       </c>
       <c r="T30" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" s="16">
         <v>0</v>
@@ -3572,13 +3528,13 @@
         <v>0</v>
       </c>
       <c r="Y30" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="16">
         <v>0</v>
       </c>
       <c r="AA30" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="16">
         <v>0</v>
@@ -3793,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="16">
         <v>0</v>
@@ -3814,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="16">
         <v>0</v>
@@ -3856,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="Z34" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" s="16">
         <v>0</v>
@@ -3896,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="16">
         <v>0</v>
@@ -3959,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA35" s="16">
         <v>0</v>
@@ -4143,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="D39" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="16">
         <v>0</v>
@@ -4164,20 +4120,20 @@
         <v>0</v>
       </c>
       <c r="K39" s="16">
+        <v>4</v>
+      </c>
+      <c r="L39" s="16">
+        <v>0</v>
+      </c>
+      <c r="M39" s="16">
+        <v>0</v>
+      </c>
+      <c r="N39" s="16">
+        <v>0</v>
+      </c>
+      <c r="O39" s="16">
         <v>1</v>
       </c>
-      <c r="L39" s="16">
-        <v>0</v>
-      </c>
-      <c r="M39" s="16">
-        <v>0</v>
-      </c>
-      <c r="N39" s="16">
-        <v>0</v>
-      </c>
-      <c r="O39" s="16">
-        <v>0</v>
-      </c>
       <c r="P39" s="16">
         <v>0</v>
       </c>
@@ -4185,16 +4141,16 @@
         <v>0</v>
       </c>
       <c r="R39" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39" s="16">
         <v>0</v>
       </c>
       <c r="T39" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" s="16">
         <v>0</v>
@@ -4206,10 +4162,10 @@
         <v>0</v>
       </c>
       <c r="Y39" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" s="16">
         <v>0</v>
@@ -4249,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="16">
         <v>0</v>
@@ -4267,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="16">
         <v>0</v>
@@ -4279,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="16">
         <v>0</v>
@@ -4297,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="U40" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" s="16">
         <v>0</v>
@@ -4309,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="Y40" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z40" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" s="16">
         <v>0</v>
@@ -4527,40 +4483,40 @@
         <v>0</v>
       </c>
       <c r="D44" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E44" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="16">
+        <v>4</v>
+      </c>
+      <c r="G44" s="16">
+        <v>3</v>
+      </c>
+      <c r="H44" s="16">
+        <v>2</v>
+      </c>
+      <c r="I44" s="16">
+        <v>0</v>
+      </c>
+      <c r="J44" s="16">
+        <v>0</v>
+      </c>
+      <c r="K44" s="16">
         <v>1</v>
       </c>
-      <c r="G44" s="16">
-        <v>0</v>
-      </c>
-      <c r="H44" s="16">
-        <v>0</v>
-      </c>
-      <c r="I44" s="16">
-        <v>0</v>
-      </c>
-      <c r="J44" s="16">
-        <v>0</v>
-      </c>
-      <c r="K44" s="16">
-        <v>0</v>
-      </c>
       <c r="L44" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" s="16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N44" s="16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O44" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P44" s="16">
         <v>0</v>
@@ -4569,16 +4525,16 @@
         <v>0</v>
       </c>
       <c r="R44" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="16">
         <v>0</v>
       </c>
       <c r="T44" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U44" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="16">
         <v>0</v>
@@ -4590,22 +4546,22 @@
         <v>0</v>
       </c>
       <c r="Y44" s="16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z44" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA44" s="16">
         <v>0</v>
       </c>
       <c r="AB44" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC44" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD44" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE44" s="16">
         <v>0</v>
@@ -4630,20 +4586,20 @@
         <v>0</v>
       </c>
       <c r="D45" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="16">
         <v>0</v>
       </c>
       <c r="F45" s="16">
+        <v>3</v>
+      </c>
+      <c r="G45" s="16">
+        <v>4</v>
+      </c>
+      <c r="H45" s="16">
         <v>1</v>
       </c>
-      <c r="G45" s="16">
-        <v>0</v>
-      </c>
-      <c r="H45" s="16">
-        <v>0</v>
-      </c>
       <c r="I45" s="16">
         <v>0</v>
       </c>
@@ -4654,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="L45" s="16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M45" s="16">
         <v>0</v>
       </c>
       <c r="N45" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O45" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" s="16">
         <v>0</v>
@@ -4678,25 +4634,25 @@
         <v>0</v>
       </c>
       <c r="T45" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" s="16">
         <v>0</v>
       </c>
       <c r="W45" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X45" s="16">
         <v>0</v>
       </c>
       <c r="Y45" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z45" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA45" s="16">
         <v>0</v>
@@ -4708,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE45" s="16">
         <v>0</v>
@@ -4911,19 +4867,19 @@
         <v>0</v>
       </c>
       <c r="D49" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E49" s="16">
         <v>0</v>
       </c>
       <c r="F49" s="16">
+        <v>2</v>
+      </c>
+      <c r="G49" s="16">
         <v>1</v>
       </c>
-      <c r="G49" s="16">
-        <v>0</v>
-      </c>
       <c r="H49" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="16">
         <v>0</v>
@@ -4932,19 +4888,19 @@
         <v>0</v>
       </c>
       <c r="K49" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M49" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P49" s="16">
         <v>0</v>
@@ -4953,16 +4909,16 @@
         <v>0</v>
       </c>
       <c r="R49" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S49" s="16">
         <v>0</v>
       </c>
       <c r="T49" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="16">
         <v>0</v>
@@ -4974,16 +4930,16 @@
         <v>0</v>
       </c>
       <c r="Y49" s="16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z49" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA49" s="16">
         <v>0</v>
       </c>
       <c r="AB49" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC49" s="16">
         <v>0</v>
@@ -5014,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="16">
         <v>0</v>
@@ -5023,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="16">
         <v>0</v>
@@ -5038,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="L50" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M50" s="16">
         <v>0</v>
       </c>
       <c r="N50" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="16">
         <v>0</v>
@@ -5056,16 +5012,16 @@
         <v>0</v>
       </c>
       <c r="R50" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S50" s="16">
         <v>0</v>
       </c>
       <c r="T50" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V50" s="16">
         <v>0</v>
@@ -5077,10 +5033,10 @@
         <v>0</v>
       </c>
       <c r="Y50" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z50" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50" s="16">
         <v>0</v>
@@ -5295,37 +5251,37 @@
         <v>0</v>
       </c>
       <c r="D54" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E54" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="16">
+        <v>8</v>
+      </c>
+      <c r="G54" s="16">
+        <v>3</v>
+      </c>
+      <c r="H54" s="16">
+        <v>3</v>
+      </c>
+      <c r="I54" s="16">
+        <v>0</v>
+      </c>
+      <c r="J54" s="16">
+        <v>0</v>
+      </c>
+      <c r="K54" s="16">
+        <v>0</v>
+      </c>
+      <c r="L54" s="16">
         <v>6</v>
       </c>
-      <c r="G54" s="16">
-        <v>0</v>
-      </c>
-      <c r="H54" s="16">
-        <v>0</v>
-      </c>
-      <c r="I54" s="16">
-        <v>0</v>
-      </c>
-      <c r="J54" s="16">
-        <v>0</v>
-      </c>
-      <c r="K54" s="16">
-        <v>0</v>
-      </c>
-      <c r="L54" s="16">
-        <v>0</v>
-      </c>
       <c r="M54" s="16">
         <v>0</v>
       </c>
       <c r="N54" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="16">
         <v>0</v>
@@ -5337,16 +5293,16 @@
         <v>0</v>
       </c>
       <c r="R54" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="16">
         <v>0</v>
       </c>
       <c r="T54" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U54" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V54" s="16">
         <v>0</v>
@@ -5358,16 +5314,16 @@
         <v>0</v>
       </c>
       <c r="Y54" s="16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z54" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA54" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC54" s="16">
         <v>0</v>
@@ -5401,13 +5357,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55" s="16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G55" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="16">
         <v>0</v>
@@ -5422,13 +5378,13 @@
         <v>0</v>
       </c>
       <c r="L55" s="16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M55" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" s="16">
         <v>0</v>
@@ -5449,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V55" s="16">
         <v>0</v>
@@ -5461,13 +5417,13 @@
         <v>0</v>
       </c>
       <c r="Y55" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z55" s="16">
         <v>0</v>
       </c>
       <c r="AA55" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" s="16">
         <v>0</v>
@@ -7622,7 +7578,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L84" s="16">
         <v>0</v>
@@ -7658,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="W84" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="16">
         <v>0</v>
@@ -7667,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="Z84" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA84" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB84" s="16">
         <v>0</v>
@@ -7713,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="16">
         <v>0</v>
@@ -7752,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="T85" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U85" s="16">
         <v>0</v>
@@ -7761,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X85" s="16">
         <v>0</v>
@@ -8027,14 +7983,14 @@
         <v>0</v>
       </c>
       <c r="R89" s="16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S89" s="16">
+        <v>0</v>
+      </c>
+      <c r="T89" s="16">
         <v>1</v>
       </c>
-      <c r="T89" s="16">
-        <v>0</v>
-      </c>
       <c r="U89" s="16">
         <v>0</v>
       </c>
@@ -8051,10 +8007,10 @@
         <v>0</v>
       </c>
       <c r="Z89" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA89" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB89" s="16">
         <v>0</v>
@@ -8076,7 +8032,7 @@
       </c>
       <c r="AH89" s="17">
         <f t="shared" ref="AH89:AH90" si="15">SUM(C89:AG89)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="32.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -8118,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="N90" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O90" s="16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P90" s="16">
         <v>0</v>
@@ -8130,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="R90" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S90" s="16">
         <v>0</v>
@@ -8154,10 +8110,10 @@
         <v>0</v>
       </c>
       <c r="Z90" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="16">
         <v>1</v>
-      </c>
-      <c r="AA90" s="16">
-        <v>0</v>
       </c>
       <c r="AB90" s="16">
         <v>0</v>
@@ -8179,7 +8135,7 @@
       </c>
       <c r="AH90" s="17">
         <f t="shared" si="15"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" ht="32.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
@@ -8390,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L94" s="16">
         <v>0</v>
@@ -8405,13 +8361,13 @@
         <v>0</v>
       </c>
       <c r="P94" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="16">
         <v>0</v>
       </c>
       <c r="R94" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" s="16">
         <v>0</v>
@@ -8420,7 +8376,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V94" s="16">
         <v>0</v>
@@ -8432,13 +8388,13 @@
         <v>0</v>
       </c>
       <c r="Y94" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z94" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA94" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB94" s="16">
         <v>0</v>
@@ -8472,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="16">
         <v>0</v>
@@ -8493,22 +8449,22 @@
         <v>0</v>
       </c>
       <c r="K95" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L95" s="16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M95" s="16">
         <v>0</v>
       </c>
       <c r="N95" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" s="16">
         <v>0</v>
       </c>
       <c r="P95" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="16">
         <v>0</v>
@@ -8523,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V95" s="16">
         <v>0</v>
@@ -8538,16 +8494,16 @@
         <v>0</v>
       </c>
       <c r="Z95" s="16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA95" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB95" s="16">
         <v>0</v>
       </c>
       <c r="AC95" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD95" s="16">
         <v>0</v>
@@ -20456,7 +20412,6 @@
   </mergeCells>
   <pageMargins left="0.708661417322835" right="0.708661417322835" top="0.24" bottom="0.24" header="0" footer="0"/>
   <pageSetup paperSize="14" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21764,11 +21719,11 @@
       </c>
       <c r="J17" s="61">
         <f>SUM(February!K84,February!K85,February!K89,February!K90,February!K94,February!K95)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="61">
         <f>SUM(February!L84,February!L85,February!L89,February!L90,February!L94,February!L95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="61">
         <f>SUM(February!M84,February!M85,February!M89,February!M90,February!M94,February!M95)</f>
@@ -21780,7 +21735,7 @@
       </c>
       <c r="N17" s="61">
         <f>SUM(February!O84,February!O85,February!O89,February!O90,February!O94,February!O95)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="61">
         <f>SUM(February!P84,February!P85,February!P89,February!P90,February!P94,February!P95)</f>
@@ -21792,11 +21747,11 @@
       </c>
       <c r="Q17" s="61">
         <f>SUM(February!R84,February!R85,February!R89,February!R90,February!R94,February!R95)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" s="61">
         <f>SUM(February!S84,February!S85,February!S89,February!S90,February!S94,February!S95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" s="61">
         <f>SUM(February!T84,February!T85,February!T89,February!T90,February!T94,February!T95)</f>
@@ -21824,11 +21779,11 @@
       </c>
       <c r="Y17" s="61">
         <f>SUM(February!Z84,February!Z85,February!Z89,February!Z90,February!Z94,February!Z95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="61">
         <f>SUM(February!AA84,February!AA85,February!AA89,February!AA90,February!AA94,February!AA95)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="61">
         <f>SUM(February!AB84,February!AB85,February!AB89,February!AB90,February!AB94,February!AB95)</f>
@@ -21856,7 +21811,7 @@
       </c>
       <c r="AG17" s="62">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="45"/>
       <c r="AI17" s="77"/>
@@ -22228,11 +22183,11 @@
       </c>
       <c r="J20" s="83">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="83">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="83">
         <f t="shared" si="1"/>
@@ -22244,7 +22199,7 @@
       </c>
       <c r="N20" s="83">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" s="83">
         <f t="shared" si="1"/>
@@ -22256,11 +22211,11 @@
       </c>
       <c r="Q20" s="83">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" s="83">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="83">
         <f t="shared" si="1"/>
@@ -22288,11 +22243,11 @@
       </c>
       <c r="Y20" s="83">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="83">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="83">
         <f t="shared" si="1"/>
@@ -22320,7 +22275,7 @@
       </c>
       <c r="AG20" s="84">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="45"/>
       <c r="AI20" s="77"/>
@@ -22742,7 +22697,7 @@
       </c>
       <c r="AP27" s="69">
         <f>SUM(AO27,AO28,AO29)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
@@ -22788,15 +22743,15 @@
       <c r="AL28" s="10"/>
       <c r="AM28" s="79">
         <f>SUM(February!AH89)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="79">
         <f>SUM(February!AH90)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="80">
         <f>SUM(February!AH89,February!AH90)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP28" s="77"/>
     </row>
@@ -23019,15 +22974,15 @@
       <c r="AL32" s="58"/>
       <c r="AM32" s="103">
         <f t="shared" ref="AM32:AO32" si="2">SUM(AM13:AM31)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="103">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="102">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP32" s="58"/>
     </row>
@@ -23168,11 +23123,11 @@
       <c r="AL35" s="10"/>
       <c r="AM35" s="108">
         <f>SUM(February!AH14,February!AH19,February!AH24,February!AH29,February!AH34,February!AH39,February!AH44,February!AH49,February!AH54,February!AH59,February!AH64,February!AH69,February!AH74,February!AH79,February!AH84,February!AH89,February!AH94,February!AH100,February!AH105)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="109">
         <f>SUM(AM35,AM36)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AO35" s="93"/>
       <c r="AP35" s="93"/>
@@ -23220,7 +23175,7 @@
       <c r="AL36" s="73"/>
       <c r="AM36" s="111">
         <f>SUM(February!AH15,February!AH20,February!AH25,February!AH30,February!AH35,February!AH40,February!AH45,February!AH50,February!AH55,February!AH60,February!AH65,February!AH70,February!AH75,February!AH80,February!AH85,February!AH90,February!AH95,February!AH101,February!AH106)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN36" s="112"/>
       <c r="AO36" s="93"/>
